--- a/artfynd/A 54517-2025 artfynd.xlsx
+++ b/artfynd/A 54517-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123041637</v>
+        <v>123056726</v>
       </c>
       <c r="B2" t="n">
-        <v>78786</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493411</v>
+        <v>493365</v>
       </c>
       <c r="R2" t="n">
-        <v>7009877</v>
+        <v>7009914</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Flera fruktkroppar i en smal granstam som lutar mot en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,6 +766,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,12 +787,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # En stående/lutande smal granstam som lutar mot en flerstammig sälg. # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,43 +810,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123057570</v>
+        <v>125755362</v>
       </c>
       <c r="B3" t="n">
-        <v>97367</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -852,13 +850,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493373</v>
+        <v>493371</v>
       </c>
       <c r="R3" t="n">
-        <v>7009844</v>
+        <v>7009937</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,12 +880,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>21:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rätt gott om fruktkroppar i en relativt grov delvis avbarkad granlåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,6 +915,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,48 +952,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123055266</v>
+        <v>123046343</v>
       </c>
       <c r="B4" t="n">
-        <v>100680</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,13 +992,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493376</v>
+        <v>493442</v>
       </c>
       <c r="R4" t="n">
-        <v>7009926</v>
+        <v>7009799</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,6 +1030,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I gammal granskog med bitvis goda mängder död ved.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1019,6 +1047,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1036,43 +1084,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123047895</v>
+        <v>123048347</v>
       </c>
       <c r="B5" t="n">
-        <v>97367</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1081,13 +1124,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493424</v>
+        <v>493416</v>
       </c>
       <c r="R5" t="n">
-        <v>7009777</v>
+        <v>7009768</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,6 +1174,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1148,58 +1211,55 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123046087</v>
+        <v>123135507</v>
       </c>
       <c r="B6" t="n">
-        <v>79896</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brynjelägden, Brynjelägden, Jmt</t>
+          <t>Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493418</v>
+        <v>493365</v>
       </c>
       <c r="R6" t="n">
-        <v>7009830</v>
+        <v>7009914</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1231,17 +1291,13 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På en yngre mer smal sälg.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1252,22 +1308,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1285,58 +1341,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123055998</v>
+        <v>123034217</v>
       </c>
       <c r="B7" t="n">
-        <v>79896</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493356</v>
+        <v>493321</v>
       </c>
       <c r="R7" t="n">
-        <v>7009932</v>
+        <v>7009835</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1368,11 +1414,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en flerstammig sälg.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1389,22 +1430,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1422,58 +1463,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123041745</v>
+        <v>123039744</v>
       </c>
       <c r="B8" t="n">
-        <v>91006</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493424</v>
+        <v>493408</v>
       </c>
       <c r="R8" t="n">
-        <v>7009866</v>
+        <v>7009898</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1531,12 +1562,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1554,67 +1585,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123057555</v>
+        <v>123041637</v>
       </c>
       <c r="B9" t="n">
-        <v>57643</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493366</v>
+        <v>493411</v>
       </c>
       <c r="R9" t="n">
-        <v>7009842</v>
+        <v>7009877</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1648,7 +1660,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1663,6 +1675,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1680,58 +1712,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123048347</v>
+        <v>123046193</v>
       </c>
       <c r="B10" t="n">
-        <v>90988</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493416</v>
+        <v>493415</v>
       </c>
       <c r="R10" t="n">
-        <v>7009768</v>
+        <v>7009815</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1763,6 +1785,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1789,12 +1816,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1812,58 +1839,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123047267</v>
+        <v>123049318</v>
       </c>
       <c r="B11" t="n">
-        <v>91006</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493446</v>
+        <v>493450</v>
       </c>
       <c r="R11" t="n">
-        <v>7009806</v>
+        <v>7009784</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1895,6 +1912,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1921,12 +1943,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1944,58 +1966,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123047649</v>
+        <v>123049755</v>
       </c>
       <c r="B12" t="n">
-        <v>91006</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493432</v>
+        <v>493474</v>
       </c>
       <c r="R12" t="n">
-        <v>7009795</v>
+        <v>7009808</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2027,11 +2039,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växer i en relativt grov stående döende gran.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2058,12 +2065,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2081,58 +2088,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123046343</v>
+        <v>123725254</v>
       </c>
       <c r="B13" t="n">
-        <v>90988</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493442</v>
+        <v>493410</v>
       </c>
       <c r="R13" t="n">
-        <v>7009799</v>
+        <v>7009704</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2156,17 +2153,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>I gammal granskog med bitvis goda mängder död ved.</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2195,12 +2187,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2221,12 +2213,7 @@
         <v>123055634</v>
       </c>
       <c r="B14" t="n">
-        <v>79867</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2350,53 +2337,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123049318</v>
+        <v>123046087</v>
       </c>
       <c r="B15" t="n">
-        <v>78786</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493450</v>
+        <v>493418</v>
       </c>
       <c r="R15" t="n">
-        <v>7009784</v>
+        <v>7009830</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2430,7 +2417,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På en yngre mer smal sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2449,22 +2436,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2482,53 +2469,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123046193</v>
+        <v>123055998</v>
       </c>
       <c r="B16" t="n">
-        <v>78786</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493415</v>
+        <v>493356</v>
       </c>
       <c r="R16" t="n">
-        <v>7009815</v>
+        <v>7009932</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2562,7 +2549,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Enstaka bålar på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2581,22 +2568,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2614,60 +2601,62 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123056726</v>
+        <v>125755405</v>
       </c>
       <c r="B17" t="n">
-        <v>91683</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>67</v>
+        <v>102999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493365</v>
+        <v>493404</v>
       </c>
       <c r="R17" t="n">
-        <v>7009914</v>
+        <v>7009887</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2691,17 +2680,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en smal granstam som lutar mot en flerstammig sälg.</t>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2710,33 +2704,12 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # En stående/lutande smal granstam som lutar mot en flerstammig sälg. # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2754,60 +2727,67 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123135507</v>
+        <v>123617140</v>
       </c>
       <c r="B18" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brynjelägden, Jmt</t>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493365</v>
+        <v>493469</v>
       </c>
       <c r="R18" t="n">
-        <v>7009914</v>
+        <v>7009816</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2831,12 +2811,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Observation i flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2845,33 +2830,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2892,12 +2856,7 @@
         <v>123617329</v>
       </c>
       <c r="B19" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3020,43 +2979,47 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123616867</v>
+        <v>123057555</v>
       </c>
       <c r="B20" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3065,13 +3028,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493384</v>
+        <v>493366</v>
       </c>
       <c r="R20" t="n">
-        <v>7009812</v>
+        <v>7009842</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3095,12 +3058,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3132,58 +3100,67 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123617207</v>
+        <v>123618504</v>
       </c>
       <c r="B21" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493466</v>
+        <v>493449</v>
       </c>
       <c r="R21" t="n">
-        <v>7009777</v>
+        <v>7009750</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3213,6 +3190,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Minst 340 st plantor och 7 st vinterståndare på en yta av ca 3 x 1 m2 inom ca 4 meters radie från fyndplatsens koordinatpunkt vid en nyligen hackspettsbearbetad stående död gran (se bild). Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3244,43 +3226,43 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123616525</v>
+        <v>123619506</v>
       </c>
       <c r="B22" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3289,13 +3271,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493367</v>
+        <v>493457</v>
       </c>
       <c r="R22" t="n">
-        <v>7009852</v>
+        <v>7009777</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3325,6 +3307,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Minst 250 st plantor och 21 st vinterståndare på en yta av ca 2 m2 på och kring en gammal överväxt stubbe. De flesta plantorna finns kring stubben. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3356,58 +3343,67 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123616609</v>
+        <v>123728604</v>
       </c>
       <c r="B23" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493390</v>
+        <v>493379</v>
       </c>
       <c r="R23" t="n">
-        <v>7009845</v>
+        <v>7009848</v>
       </c>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3431,12 +3427,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minst 410 st plantor och 8 st vinterståndare på en yta av ca 5 x 1 m2 inom ca 5 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3468,40 +3469,44 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123732971</v>
+        <v>123732177</v>
       </c>
       <c r="B24" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -3518,10 +3523,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493336</v>
+        <v>493430</v>
       </c>
       <c r="R24" t="n">
-        <v>7009883</v>
+        <v>7009898</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3554,6 +3559,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minst 300 st plantor och 1 st vinterståndare på en yta av ca 4 x 0,5 m2 inom ca 6 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3585,48 +3595,47 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123732386</v>
+        <v>124501251</v>
       </c>
       <c r="B25" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3635,10 +3644,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493374</v>
+        <v>493356</v>
       </c>
       <c r="R25" t="n">
-        <v>7009884</v>
+        <v>7009863</v>
       </c>
       <c r="S25" t="n">
         <v>8</v>
@@ -3665,12 +3674,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3702,63 +3726,62 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123727458</v>
+        <v>124503702</v>
       </c>
       <c r="B26" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493403</v>
+        <v>493353</v>
       </c>
       <c r="R26" t="n">
-        <v>7009782</v>
+        <v>7009865</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3782,12 +3805,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3819,72 +3857,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123618504</v>
+        <v>123047895</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493449</v>
+        <v>493424</v>
       </c>
       <c r="R27" t="n">
-        <v>7009750</v>
+        <v>7009777</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3908,17 +3927,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minst 340 st plantor och 7 st vinterståndare på en yta av ca 3 x 1 m2 inom ca 4 meters radie från fyndplatsens koordinatpunkt vid en nyligen hackspettsbearbetad stående död gran (se bild). Fyndplatsen finns i gammal granskog.</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3950,48 +3964,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123619506</v>
+        <v>123057570</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4000,13 +4004,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493457</v>
+        <v>493373</v>
       </c>
       <c r="R28" t="n">
-        <v>7009777</v>
+        <v>7009844</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4030,17 +4034,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Minst 250 st plantor och 21 st vinterståndare på en yta av ca 2 m2 på och kring en gammal överväxt stubbe. De flesta plantorna finns kring stubben. Fyndplatsen finns i gammal granskog.</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4072,72 +4071,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123728604</v>
+        <v>123617207</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493379</v>
+        <v>493466</v>
       </c>
       <c r="R29" t="n">
-        <v>7009848</v>
+        <v>7009777</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4161,17 +4141,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 410 st plantor och 8 st vinterståndare på en yta av ca 5 x 1 m2 inom ca 5 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4203,15 +4178,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124503013</v>
+        <v>125757311</v>
       </c>
       <c r="B30" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4219,24 +4189,33 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -4248,13 +4227,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493421</v>
+        <v>493445</v>
       </c>
       <c r="R30" t="n">
-        <v>7009797</v>
+        <v>7009875</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4278,22 +4257,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>17:12</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>17:12</t>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 3 plantor inom ca 0,2 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4325,64 +4299,55 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124501251</v>
+        <v>123055266</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493356</v>
+        <v>493376</v>
       </c>
       <c r="R31" t="n">
-        <v>7009863</v>
+        <v>7009926</v>
       </c>
       <c r="S31" t="n">
         <v>8</v>
@@ -4409,27 +4374,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4461,49 +4411,35 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124503702</v>
+        <v>123616525</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4515,10 +4451,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493353</v>
+        <v>493367</v>
       </c>
       <c r="R32" t="n">
-        <v>7009865</v>
+        <v>7009852</v>
       </c>
       <c r="S32" t="n">
         <v>7</v>
@@ -4545,27 +4481,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>17:24</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4597,38 +4518,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755362</v>
+        <v>123616609</v>
       </c>
       <c r="B33" t="n">
-        <v>91538</v>
+        <v>101326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4637,10 +4558,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493371</v>
+        <v>493390</v>
       </c>
       <c r="R33" t="n">
-        <v>7009937</v>
+        <v>7009845</v>
       </c>
       <c r="S33" t="n">
         <v>11</v>
@@ -4667,27 +4588,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>21:35</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rätt gott om fruktkroppar i en relativt grov delvis avbarkad granlåga.</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4702,26 +4608,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4739,47 +4625,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755405</v>
+        <v>123616867</v>
       </c>
       <c r="B34" t="n">
-        <v>58089</v>
+        <v>101326</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102999</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4788,13 +4665,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493404</v>
+        <v>493384</v>
       </c>
       <c r="R34" t="n">
-        <v>7009887</v>
+        <v>7009812</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4818,22 +4695,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>21:40</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>21:40</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4862,6 +4729,897 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>123727458</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>493403</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7009782</v>
+      </c>
+      <c r="S35" t="n">
+        <v>11</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>123730921</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>493438</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7009868</v>
+      </c>
+      <c r="S36" t="n">
+        <v>11</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>123732386</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>493374</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7009884</v>
+      </c>
+      <c r="S37" t="n">
+        <v>8</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>123732971</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>493336</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7009883</v>
+      </c>
+      <c r="S38" t="n">
+        <v>9</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>124500585</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>493320</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7009826</v>
+      </c>
+      <c r="S39" t="n">
+        <v>9</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>124503013</v>
+      </c>
+      <c r="B40" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>493421</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7009797</v>
+      </c>
+      <c r="S40" t="n">
+        <v>7</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125757252</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>493446</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7009874</v>
+      </c>
+      <c r="S41" t="n">
+        <v>8</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>125757664</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>493365</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7009973</v>
+      </c>
+      <c r="S42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54517-2025 artfynd.xlsx
+++ b/artfynd/A 54517-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -807,6 +812,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123056726</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -949,6 +959,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755362</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1081,6 +1096,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123046343</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1208,6 +1228,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123048347</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1338,6 +1363,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123135507</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1460,6 +1490,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123034217</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1582,6 +1617,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123039744</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1709,6 +1749,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123041637</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1836,6 +1881,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123046193</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1963,6 +2013,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123049318</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2085,6 +2140,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123049755</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2207,6 +2267,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123725254</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2334,6 +2399,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123055634</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2466,6 +2536,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123046087</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2598,6 +2673,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123055998</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2724,6 +2804,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755405</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2850,6 +2935,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617140</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2976,6 +3066,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617329</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3097,6 +3192,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123057555</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3223,6 +3323,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123618504</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3340,6 +3445,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123619506</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3466,6 +3576,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123728604</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3592,6 +3707,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123732177</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3723,6 +3843,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124501251</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3854,6 +3979,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124503702</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3961,6 +4091,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123047895</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4068,6 +4203,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123057570</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4175,6 +4315,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617207</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4296,6 +4441,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125757311</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4408,6 +4558,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123055266</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4515,6 +4670,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123616525</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4622,6 +4782,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123616609</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4729,6 +4894,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123616867</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4841,6 +5011,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123727458</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4953,6 +5128,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123730921</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5065,6 +5245,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123732386</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5177,6 +5362,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123732971</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5294,6 +5484,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124500585</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5411,6 +5606,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124503013</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5518,6 +5718,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125757252</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5620,8 +5825,56 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125757664</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>